--- a/data_extactor/batch_10_fa/batch_0082_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0082_fa.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار ایمیل | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | RepairTRAX | نرم‌افزار کنترل فرایند آماری SPC</t>
+          <t>نرم‌افزار ایمیل | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Word | RepairTRAX | نرم‌افزار کنترل فرآیند آماری SPC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | کامپیوتر و الکترونیک | خدمات مشتریان و شخصی | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>بینایی نزدیک | تجسم | زبردستی انگشتان | ثبات دست و بازو | حساسیت به مشکل | درک کتبی | زبردستی دستی | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | دقت کنترل | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | تجسم | مهارت انگشتان | ثبات دست و بازو | حساسیت به مسئله | درک کتبی | مهارت دستی | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | دقت کنترل | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | داخل ساختمان، با تهویه مطبوع | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | ایمیل | مکالمات تلفنی | فشار زمانی</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | ایمیل | مکالمات تلفنی | فشار زمانی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و فناوری‌شناسان مهندسی هوافضا و عملیات | مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | نصاب‌ها و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های اویونیک | تکنسین‌ها و فناوری‌شناسان کالیبراسیون | تعمیرکاران کامپیوتر، خودپرداز و ماشین‌های اداری | تکنسین‌ها و فناوری‌شناسان مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک تجهیزات تجاری و صنعتی | تکنسین‌ها و فناوری‌شناسان الکترومکانیک و مکاترونیک | مونتاژکنندگان تجهیزات الکترومکانیکی | نصاب‌ها و تعمیرکاران تجهیزات الکترونیکی وسایل نقلیه موتوری | تکنسین‌های نورپردازی | تعمیرکاران تجهیزات پزشکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده فلز و پلاستیک | آپاراتچی‌های سینما | تکنسین‌های آزمایشگاه چشم‌پزشکی | کارگران فرآیند عکاسی و اپراتورهای ماشین‌های پردازش | تکنسین‌های فوتونیک | تکنسین‌ها و کارگران پیش از چاپ | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصب‌کنندگان و تعمیرکنندگان تجهیزات صوتی و تصویری | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | تکنسین‌های نورپردازی | تعمیرکاران تجهیزات پزشکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | آپاراتچی‌های سینما | تکنسین‌های آزمایشگاه چشم‌پزشکی | کارگران فرآیندهای عکاسی و اپراتورهای ماشین‌های فرآوری | تکنسین‌های فوتونیک | تکنسین‌ها و کارگران پیش از چاپ | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>نرم‌افزار سیستم مدیریت نگهداری کامپیوتری CMMS | FaceTime | نرم‌افزار سیستم کنترل موجودی | نرم‌افزار تشخیص تجهیزات پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | نرم‌افزار Salesforce | نرم‌افزار مرورگر وب</t>
+          <t>سیستم مدیریت نگهداری کامپیوتری CMMS | FaceTime | نرم‌افزار سیستم کنترل موجودی | نرم‌افزار تشخیص تجهیزات پزشکی | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار SAP | نرم‌افزار Salesforce | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -570,22 +570,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | کامپیوتر و الکترونیک | خدمات مشتریان و شخصی | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | بینایی نزدیک | زبردستی انگشتان | استدلال قیاسی | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تجسم | ثبات دست و بازو | زبردستی دستی | تشخیص رنگ بصری | دقت کنترل | درک شفاهی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری گسترده | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | مهارت انگشتان | استدلال قیاسی | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تجسم | ثبات دست و بازو | مهارت دستی | تشخیص رنگ بصری | دقت کنترل | درک شفاهی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | داخل ساختمان، با تهویه مطبوع | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | ارتباط با دیگران | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | نزدیکی فیزیکی | صرف زمان برای ایستادن | پیامد اشتباه</t>
+          <t>اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | مکالمات تلفنی | ارتباط با دیگران | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | نزدیکی فیزیکی | صرف زمان برای ایستادن | پیامد خطا</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و فناوری‌شناسان مهندسی هوافضا و عملیات | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | مهندسان زیستی و مهندسان زیست‌پزشکی | تکنسین‌ها و فناوری‌شناسان کالیبراسیون | تعمیرکاران کامپیوتر، خودپرداز و ماشین‌های اداری | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و فناوری‌شناسان مهندسی برق و الکترونیک | نصاب‌ها و تعمیرکاران برق و الکترونیک تجهیزات حمل و نقل | تعمیرکاران برق و الکترونیک تجهیزات تجاری و صنعتی | مونتاژکنندگان تجهیزات الکترومکانیکی | تکنسین‌ها و فناوری‌شناسان مهندسی صنایع | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و تعمیرات عمومی | تکنسین‌ها و فناوری‌شناسان مهندسی مکانیک | تکنسین‌های وسایل پزشکی | آماده‌سازان تجهیزات پزشکی | تکنسین‌ها و فناوری‌شناسان مهندسی فناوری نانو | تکنسین‌های فوتونیک | تکنسین‌های رباتیک</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های هوانوردی | مهندسان زیستی و مهندسان زیست‌پزشکی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | تکنسین‌ها و کارشناسان مهندسی صنایع | مکانیک‌های ماشین‌آلات صنعتی | کارگران نگهداری و تعمیرات عمومی | تکنسین‌ها و کارشناسان مهندسی مکانیک | تکنسین‌های تجهیزات پزشکی | آماده‌سازان تجهیزات پزشکی | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مکانیک | هنرهای زیبا | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مکانیک | هنرهای زیبا | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت شنوایی | ثبات دست و بازو | زبردستی دستی | زبردستی انگشتان | بینایی نزدیک | دقت کنترل | توجه شنوایی | تجسم | حساسیت به مشکل | استدلال قیاسی | انعطاف‌پذیری بستار | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک شفاهی | بیان شفاهی | درک کتبی | بینایی دور | هماهنگی چندعضوی | سرعت بستار</t>
+          <t>حساسیت شنوایی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | توجه شنیداری | تجسم | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری بستار | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک شفاهی | بیان شفاهی | درک کتبی | بینایی دور | هماهنگی چند عضو | سرعت بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | ایمیل | داخل ساختمان، با تهویه مطبوع | آزادی در تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | فشار زمانی | برخورد با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان</t>
+          <t>اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فشار زمانی | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | تکنسین‌ها و فناوری‌شناسان کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکنندگان تجهیزات الکترومکانیکی | مونتاژکنندگان موتور و سایر ماشین‌آلات | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش فلز و پلاستیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | کارگران ورق‌کاری | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تیزکنندگان، سوهان‌کاران و پرداخت‌کاران ابزار | تعمیرکاران ساعت مچی و دیواری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات صنایع چوب، به جز اره‌کاری</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | کارگران ورق‌کاری | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تعمیرکاران ساعت مچی و دیواری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های چوب‌بری، به جز اره‌کشی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و شخصی | مدیریت و سازماندهی | مکانیک | اداری | مهندسی و فناوری | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | مکانیک | اداری | مهندسی و فناوری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>زبردستی انگشتان | ثبات دست و بازو | دقت کنترل | بینایی نزدیک | زبردستی دستی | ترتیب‌دهی اطلاعات | حساسیت به مشکل | تجسم | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت دستی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تجسم | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی, کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | داخل ساختمان، با تهویه مطبوع | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | ارتباط با دیگران | نزدیکی فیزیکی | فراوانی تصمیم‌گیری</t>
+          <t>صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | فشار زمانی | ارتباط با دیگران | نزدیکی فیزیکی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تعمیرکاران دوربین و تجهیزات عکاسی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایس | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج فلز و پلاست | کارگران سنگ‌زنی و پولیش دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاست | مکانیک‌های ماشین‌آلات صنعتی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش فلز و پلاست | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده فلز و پلاست | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاست | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های ریسندگی، تابندگی و کشش منسوجات | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | تیزکنندگان، سوهان‌کاران و پرداخت‌کاران ابزار</t>
+          <t>تعمیرکاران دوربین و تجهیزات عکاسی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | سرویس‌کاران و تعمیرکاران ماشین‌های سکه‌ای، فروش خودکار و تفریحی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و ورقه‌کن | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورج، فلز و پلاستیک | کارگران سنگ‌زنی و پرداخت دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | جواهرسازان و کارگران سنگ‌ها و فلزات قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین بوبین‌پیچی، تابندگی و کشش منسوجات | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,32 +731,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | نرم‌افزار شبیه‌سازی ANSYS | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | نرم‌افزار طراحی سه بعدی 3D کامپیوتری CAD | نرم‌افزار طراحی دو بعدی 2D کامپیوتری CAD | نرم‌افزار ایمیل | Microsoft PowerPoint | نرم‌افزار سیستم مدیریت نگهداری کامپیوتری CMMS</t>
+          <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | نرم‌افزار شبیه‌سازی ANSYS | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | نرم‌افزار طراحی سه بعدی به کمک کامپیوتر CAD | نرم‌افزار طراحی دو بعدی به کمک کامپیوتر CAD | نرم‌افزار ایمیل | Microsoft PowerPoint | سیستم مدیریت نگهداری کامپیوتری CMMS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | پایش | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | کامپیوتر و الکترونیک | مهندسی و فناوری | ریاضیات | زبان انگلیسی | فیزیک | طراحی | خدمات مشتریان و شخصی</t>
+          <t>مکانیک | رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | زبان انگلیسی | فیزیک | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مشکل | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | زبردستی انگشتان | زبردستی دستی | دقت کنترل | هماهنگی چندعضوی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، با تهویه مطبوع | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | پیامد اشتباه | داخل ساختمان، بدون تهویه مطبوع | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارگران</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | پیامد خطا | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | صرف زمان برای انجام حرکات تکراری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض تجهیزات خطرناک | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران تجهیزات پزشکی | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تعمیرکاران ساعت مچی و دیواری | تکنسین‌ها و فناوری‌شناسان کالیبراسیون | تعمیرکاران برق و الکترونیک تجهیزات تجاری و صنعتی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تکنسین‌های اویونیک | تعمیرکاران کامپیوتر، خودپرداز و ماشین‌های اداری | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | قفل‌سازان و تعمیرکاران گاوصندوق | تکنسین‌ها و فناوری‌شناسان مهندسی برق و الکترونیک | تکنسین‌ها و فناوری‌شناسان مهندسی مکانیک | تکنسین‌ها و فناوری‌شناسان مهندسی، به جز نقشه‌کشان، سایر | سرپرستان خط اول مکانیک‌ها، نصاب‌ها و تعمیرکاران | کارگران نصب، نگهداری و تعمیرات، سایر | بازرسان، تست‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | تکنسین‌های آزمایشگاه چشم‌پزشکی</t>
+          <t>تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران تجهیزات پزشکی | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تعمیرکاران ساعت مچی و دیواری | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تکنسین‌های هوانوردی | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | قفل‌سازان و تعمیرکاران گاوصندوق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان مهندسی مکانیک | تکنولوژیست‌ها و تکنسین‌های مهندسی، به جز نقشه‌کش‌ها، سایر موارد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | کارگران نصب، نگهداری و تعمیرات، سایر | بازرسان، آزمایش‌کنندگان، سورترها، نمونه‌برداران و توزین‌کنندگان | تکنسین‌های آزمایشگاه چشم‌پزشکی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Apple macOS | Autodesk AutoCAD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار سیستم مدیریت نگهداری کامپیوتری CMMS | سیستم‌های کامپیوتری مدیریت زمان | Dassault Systemes CATIA | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار مدیریت انرژی کنترل مستقیم دیجیتال DDC | Dropbox | Eko | FaceTime | Facebook | Google Docs | GroupMe | نرم‌افزار دستگاه‌های کامپیوتری دستی | IBM Notes | Linux | Loom | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | National Instruments LabVIEW | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | نرم‌افزار مرورگر وب | نرم‌افزار Yardi | YouTube</t>
+          <t>Apple macOS | Autodesk AutoCAD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | سیستم مدیریت نگهداری کامپیوتری CMMS | سیستم‌های مدیریت زمان رایانه‌ای | Dassault Systemes CATIA | نرم‌افزار ورود داده | نرم‌افزار پایگاه داده | نرم‌افزار مدیریت انرژی کنترل مستقیم دیجیتال DDC | Dropbox | Eko | FaceTime | Facebook | Google Docs | GroupMe | نرم‌افزار دستگاه‌های کامپیوتر جیبی | IBM Notes | Linux | Loom | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Windows | Microsoft Word | National Instruments LabVIEW | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | نرم‌افزار SAP | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | نرم‌افزار مرورگر وب | نرم‌افزار Yardi | YouTube</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | پایش | سخن گفتن | گوش دادن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ترتیب‌دهی اطلاعات | ثبات دست و بازو | زبردستی دستی | بینایی نزدیک | حساسیت به مشکل | دقت کنترل | تجسم | بیان شفاهی | درک شفاهی | استدلال قیاسی | زبردستی انگشتان | هماهنگی چندعضوی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری گسترده | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | تشخیص رنگ بصری | بینایی دور | تعادل عمومی بدن | هماهنگی عمومی بدن | قدرت تنه | قدرت ایستا | سرعت ادراکی | درک کتبی | حساسیت شنوایی</t>
+          <t>ترتیب‌دهی اطلاعات | ثبات دست و بازو | مهارت دستی | بینایی نزدیک | حساسیت به مسئله | دقت کنترل | تجسم | بیان شفاهی | درک شفاهی | استدلال قیاسی | مهارت انگشتان | هماهنگی چند عضو | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | تشخیص رنگ بصری | بینایی دور | تعادل کلی بدن | هماهنگی کلی بدن | قدرت تنه | قدرت ایستا | سرعت ادراکی | درک کتبی | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | سلامت و ایمنی سایر کارگران | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | داخل ساختمان، بدون تهویه مطبوع | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | داخل ساختمان، با تهویه مطبوع | فشار زمانی | صرف زمان برای خم شدن یا چرخاندن بدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | برخورد با مشتریان خارجی یا عموم مردم</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | مکالمات تلفنی | سلامت و ایمنی سایر کارکنان | ایمیل | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | فضای باز، در معرض تمام شرایط آب و هوایی | قرار گرفتن در معرض تجهیزات خطرناک | فراوانی تصمیم‌گیری | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای ایستادن | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای راه رفتن یا دویدن | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض آلاینده‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | محیط داخلی، بدون کنترل شرایط محیطی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | صرف زمان برای خم کردن یا چرخاندن بدن | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | تعامل با مشتریان خارجی یا عموم مردم</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | دیگ‌سازان | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصاب‌ها و تعمیرکاران برق و الکترونیک تجهیزات حمل و نقل | تعمیرکاران برق و الکترونیک تجهیزات تجاری و صنعتی | مونتاژکنندگان موتور و سایر ماشین‌آلات | مدیران تاسیسات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | مکانیک‌ها و نصاب‌های گرمایش، تهویه مطبوع و تبرید | کمک‌برق‌کاران | کارگران کمکی--نصب، نگهداری و تعمیرات | کارگران کمکی--لوله‌کش‌ها، لوله‌کش‌های صنعتی، لوله‌کش‌های گاز و بخار | تکنسین‌های نیروگاه‌های برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | سازندگان آسیاب (میل‌رایت‌ها) | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کش‌ها، لوله‌کش‌های صنعتی و لوله‌کش‌های بخار | مهندسان تاسیسات ثابت و اپراتورهای دیگ بخار</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | دیگ‌سازان | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران موتور و سایر ماشین‌آلات | مدیران تسهیلات | مکانیک‌ها و تکنسین‌های خدمات تجهیزات کشاورزی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | تکنسین‌های نیروگاه برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | مهندسان نصب ماشین‌آلات | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,32 +845,32 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار تشخیص کامپیوتری | نرم‌افزار سیستم مدیریت نگهداری کامپیوتری CMMS | IBM Maximo Asset Management | نرم‌افزار سیستم‌های کنترل صنعتی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Vestas Wind Systems A/S Vestas Remote Panel | نرم‌افزار مرورگر وب</t>
+          <t>نرم‌افزار تشخیص کامپیوتری | سیستم مدیریت نگهداری کامپیوتری CMMS | IBM Maximo Asset Management | نرم‌افزار سیستم‌های کنترل صنعتی | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | نرم‌افزار کنترل‌کننده منطقی قابل برنامه‌ریزی PLC | نرم‌افزار SAP | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Vestas Wind Systems A/S Vestas Remote Panel | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | پایش | یادگیری فعال | گوش دادن فعال | سخن گفتن | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | کامپیوتر و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | مهندسی و فناوری | آموزش و تربیت | مدیریت و سازماندهی | ریاضیات | ساختمان و ساخت‌وساز | فیزیک</t>
+          <t>مکانیک | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | مهندسی و فناوری | آموزش و پرورش | مدیریت و اداره | ریاضیات | ساختمان و ساخت‌وساز | فیزیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | درک شفاهی | زبردستی انگشتان | بینایی نزدیک | ثبات دست و بازو | زبردستی دستی | استدلال قیاسی | دقت کنترل | هماهنگی چندعضوی | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تجسم | بینایی دور | تعادل عمومی بدن | انعطاف‌پذیری گسترده | قدرت تنه | قدرت پویا | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنوایی | استقامت | قدرت ایستا | زمان عکس‌العمل | بیان کتبی</t>
+          <t>حساسیت به مسئله | درک شفاهی | مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | استدلال قیاسی | دقت کنترل | هماهنگی چند عضو | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تجسم | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت پویا | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | استقامت | قدرت ایستا | زمان عکس‌العمل | بیان کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض شرایط خطرناک | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | داخل ساختمان، بدون تهویه مطبوع | پیامد اشتباه | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | ایمیل | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای خم شدن یا چرخاندن بدن | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | فضای باز، زیر سقف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | صرف زمان برای ایستادن | تاثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | صرف زمان برای حفظ یا بازیابی تعادل | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای زانو زدن، خم شدن، دولا شدن یا خزیدن | سطح رقابت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض ارتفاعات بالا | قرار گرفتن در معرض شرایط خطرناک | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | محیط داخلی، بدون کنترل شرایط محیطی | پیامد خطا | فضای باز، در معرض تمام شرایط آب و هوایی | ایمیل | ارتباط با دیگران | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض تجهیزات خطرناک | صرف زمان برای خم کردن یا چرخاندن بدن | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | قرار گرفتن در معرض آلاینده‌ها | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | صرف زمان برای انجام حرکات تکراری | فضای باز، زیر سقف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | فشار زمانی | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | صرف زمان برای ایستادن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | مکالمات تلفنی | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای بالا رفتن از نردبان‌ها، داربست‌ها یا تیرها | صرف زمان برای حفظ یا بازیابی تعادل | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای زانو زدن، چمباتمه زدن، خم شدن یا خزیدن | سطح رقابت | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های اویونیک | تکنسین‌های نیروگاه زیست‌توده | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مهندسان برق | تعمیرکاران برق و الکترونیک نیروگاه، پست برق و رله | اپراتورهای نیروگاه گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران تولید نیروگاه‌های برق‌آبی | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | نصاب‌های خورشیدی فتوولتائیک | نصاب‌ها و تکنسین‌های حرارتی خورشیدی | مهندسان تاسیسات ثابت و اپراتورهای دیگ بخار | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | مدیران عملیات انرژی بادی</t>
+          <t>تکنسین‌های هوانوردی | تکنسین‌های نیروگاه زیست‌توده | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مهندسان برق | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، نیروگاه‌ها، پست‌های برق و رله‌ها | اپراتورهای واحدهای گاز | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان تاسیسات و اپراتورهای دیگ بخار | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | مدیران عملیات انرژی بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>پایش | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | مکانیک | خدمات مشتریان و شخصی | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | مکانیک | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>زبردستی دستی | زبردستی انگشتان | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | ترتیب‌دهی اطلاعات | هماهنگی چندعضوی | تجسم | استدلال استقرایی | استدلال قیاسی | حساسیت به مشکل | بیان شفاهی | درک شفاهی | توجه انتخابی | درک کتبی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | تجسم | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | درک کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>آزادی در تصمیم‌گیری | ایمیل | مکالمات تلفنی | ارتباط با دیگران | داخل ساختمان، با تهویه مطبوع | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
+          <t>آزادی در تصمیم‌گیری | ایمیل | مکالمات تلفنی | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت تکرار وظایف یکسان | اهمیت دقیق یا درست بودن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تعمیرکاران کامپیوتر، خودپرداز و ماشین‌های اداری | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکنندگان تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و فشرده‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاست | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای تراش فلز و پلاست | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رنده فلز و پلاست | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندگانه فلز و پلاست | اپراتورهای ماشین‌های اداری، به جز کامپیوتر | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان, اپراتورها و متصدیان ماشین‌آلات محصولات کاغذی | تیزکنندگان، سوهان‌کاران و پرداخت‌کاران ابزار | تعمیرکاران ساعت مچی و دیواری</t>
+          <t>اپراتورها و متصدیان ماشین‌های اتصال چسبی | تعمیرکاران کامپیوتر، عابربانک و ماشین‌های اداری | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن، شکل‌دهی، پرس و متراکم‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات سنگ‌زنی، لپینگ، پرداخت و صیقل‌کاری فلز و پلاستیک | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات فرزکاری و صفحه‌تراشی فلز و پلاستیک | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | تنظیم‌کنندگان، اپراتورها و متصدیان چندین ماشین‌ابزار، فلز و پلاستیک | اپراتورهای ماشین‌های اداری، به جز رایانه | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تولید محصولات کاغذی | سنگ‌زنان، سوهان‌کاران و تیزکنندگان ابزار | تعمیرکاران ساعت مچی و دیواری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | پایش | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و ساخت‌وساز | فیزیک | خدمات مشتریان و شخصی | ریاضیات | ایمنی و امنیت عمومی | آموزش و تربیت</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | فیزیک | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مشکل | ثبات دست و بازو | دقت کنترل | هماهنگی چندعضوی | زبردستی دستی | زبردستی انگشتان | بینایی نزدیک | تشخیص گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری گسترده | سرعت ادراکی | درک کتبی | انعطاف‌پذیری بستار | قدرت ایستا | بینایی دور | درک عمق | وضوح گفتار | تشخیص رنگ بصری | استقامت | قدرت تنه | زمان عکس‌العمل | اشتراک زمانی | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | قدرت پویا | جهت‌گیری پاسخ | جهت‌گیری فضایی | اصالت | روان بودن ایده‌ها | بیان کتبی | تعادل عمومی بدن | هماهنگی عمومی بدن</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | تشخیص گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری دامنه حرکت | سرعت ادراکی | درک کتبی | انعطاف‌پذیری بستار | قدرت ایستا | بینایی دور | درک عمق | وضوح گفتار | تشخیص رنگ بصری | استقامت | قدرت تنه | زمان عکس‌العمل | تقسیم توجه | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | قدرت پویا | جهت‌گیری پاسخ | جهت‌گیری فضایی | اصالت | روانی ایده‌ها | بیان کتبی | تعادل کلی بدن | هماهنگی کلی بدن</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارگران | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | پیامدهای کاری و نتایج سایر کارگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | پیامد اشتباه | تاثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات محافظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | داخل ساختمان، بدون تهویه مطبوع | فراوانی تصمیم‌گیری</t>
+          <t>استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | فضای باز، در معرض تمام شرایط آب و هوایی | ارتباط با دیگران | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | سلامت و ایمنی سایر کارکنان | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | نزدیکی فیزیکی | پیامد خطا | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | قرار گرفتن در معرض آلاینده‌ها | صرف زمان برای ایستادن | محیط داخلی، بدون کنترل شرایط محیطی | فراوانی تصمیم‌گیری</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دیگ‌سازان | کارگران ساختمانی | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و دراگ‌لاین، معدن‌کاری سطحی | کمک‌برق‌کاران | کارگران کمکی--لوله‌کش‌ها، لوله‌کش‌های صنعتی، لوله‌کش‌های گاز و بخار | اپراتورهای بالابر و وینچ | مهندسان دریا و معماران دریایی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | اپراتورهای مهندسی و سایر تجهیزات ساخت‌وساز | لوله‌گذاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و لوله‌کش‌های بخار | دکل‌بندها (ریگرها) | اپراتورهای مته چرخشی، نفت و گاز | کارگران ساده نفت و گاز | ملوانان و روغن‌کاران دریا | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | مهندسان کشتی | جوشکاران، برش‌دهندگان، لحیم‌کاران و برنج‌کاران</t>
+          <t>دیگ‌سازان | کارگران ساختمانی | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری و بارگیری و درگ‌لاین، معدن‌کاری سطحی | دستیاران--برق‌کاران | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | اپراتورهای بالابر و وینچ | مهندسان دریایی و معماران کشتی | مکانیک‌های تجهیزات سنگین متحرک، به جز موتورها | مهندسان بهره‌برداری و سایر اپراتورهای تجهیزات ساختمانی | لوله‌گذاران | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | ریگرها | اپراتورهای مته چرخشی، نفت و گاز | کارگران فنی همه‌کاره نفت و گاز | ملوانان و روغن‌کاران دریایی | سرویس‌کاران سپتیک تانک و پاک‌کنندگان لوله‌های فاضلاب | مهندسان کشتی | جوشکاران، برش‌کاران، لحیم‌کاران نرم و لحیم‌کاران سخت</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | مدیریت و سازماندهی | قانون و دولت | فروش و بازاریابی | آموزش و تربیت | ریاضیات | کامپیوتر و الکترونیک | اداری | اقتصاد و حسابداری | ساختمان و ساخت‌وساز</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | مدیریت و اداره | قانون و دولت | فروش و بازاریابی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | اداری | اقتصاد و حسابداری | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | بینایی نزدیک | زبردستی انگشتان | تجسم | دقت کنترل | بیان شفاهی | زبردستی دستی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مشکل | درک شفاهی | استدلال استقرایی | بیان کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری گسترده | قدرت تنه | هماهنگی چندعضوی</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت انگشتان | تجسم | دقت کنترل | بیان شفاهی | مهارت دستی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | استدلال استقرایی | بیان کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | اهمیت دقیق یا درست بودن | بحث‌های چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، قرار گرفتن در معرض تمام شرایط آب و هوایی | درون یک وسیله نقلیه محصور یا کار با تجهیزات محصور | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | پوشیدن تجهیزات محافظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | داخل ساختمان، بدون تهویه مطبوع | فشار زمانی | نامه‌ها و یادداشت‌های مکتوب | فضای باز، زیر سقف | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | تعیین وظایف، اولویت‌ها و اهداف | داخل ساختمان، با تهویه مطبوع | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده</t>
+          <t>مکالمات تلفنی | ایمیل | ارتباط با دیگران | اهمیت دقیق یا درست بودن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | محیط داخلی، بدون کنترل شرایط محیطی | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فضای باز، زیر سقف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکنندگان سازه، سطوح، تجهیزات پرواز و سیستم‌های هواپیما | نصاب‌ها و تعمیرکاران شیشه خودرو | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصاب‌ها و تعمیرکاران برق و الکترونیک تجهیزات حمل و نقل | برق‌کاران | نصاب‌ها و تعمیرکاران تجهیزات الکترونیکی وسایل نقلیه موتوری | نصاب‌ها و تعمیرکاران آسانسور و پله برقی | مونتاژکنندگان موتور و سایر ماشین‌آلات | کمک‌برق‌کاران | کارگران کمکی--نصب، نگهداری و تعمیرات | کارگران کمکی--لوله‌کش‌ها، لوله‌کش‌های صنعتی، لوله‌کش‌های گاز و بخار | تعمیرکاران لوازم خانگی | کارگران نگهداری و تعمیرات عمومی | تعمیرکاران درب‌های مکانیکی | سازندگان آسیاب (میل‌رایت‌ها) | لوله‌کش‌ها، لوله‌کش‌های صنعتی و لوله‌کش‌های بخار | دکل‌بندها (ریگرها) | نصاب‌های سیستم‌های امنیتی و اعلام حریق | مونتاژکنندگان و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی</t>
+          <t>مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | نصب‌کنندگان و تعمیرکنندگان شیشه خودرو | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | تعمیرکاران موتور الکتریکی، ابزار برقی و موارد مرتبط | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات حمل و نقل | برق‌کاران | نصب‌کنندگان و تعمیرکنندگان تجهیزات الکترونیکی، وسایل نقلیه موتوری | نصابان و تعمیرکاران آسانسور و پله برقی | مونتاژکاران موتور و سایر ماشین‌آلات | دستیاران--برق‌کاران | دستیاران--کارگران نصب، نگهداری و تعمیرات | دستیاران--لوله‌کشان، لوله‌کشان صنعتی و بخار | تعمیرکاران لوازم خانگی | کارگران نگهداری و تعمیرات عمومی | تعمیرکاران درب‌های مکانیکی | مهندسان نصب ماشین‌آلات | لوله‌کش‌ها، لوله‌کش‌های صنعتی و بخار | ریگرها | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | مونتاژکاران و تنظیم‌کنندگان دستگاه‌های زمان‌سنجی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0082_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0082_fa.xlsx
@@ -503,22 +503,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>RepairTRAX | نرم‌افزار کنترل فرایند آماری SPC | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Word | نرم‌افزار ایمیل</t>
+          <t>نرم‌افزار ایمیل | نرم‌افزار کنترل فرایند آماری SPC | نرم‌افزار Microsoft Office | Microsoft Excel | Microsoft Word | نرم‌افزار کنترل فرآیند آماری SPC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مهندسی و فناوری</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>دید نزدیک | تجسم فضایی | چابکی انگشتان | ثبات دست و بازو | حساسیت به مسئله | درک کتبی | چابکی دستی | توجه انتخابی | مرتب‌سازی اطلاعات | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | تمایز رنگ‌ها | دید دور | دقت کنترل | بیان شفاهی | درک شفاهی</t>
+          <t>بینایی نزدیک | تجسم | مهارت انگشتان | ثبات دست و بازو | حساسیت به مسئله | درک کتبی | مهارت دستی | توجه انتخابی | ترتیب‌دهی اطلاعات | استدلال استقرایی | استدلال قیاسی | وضوح گفتار | تشخیص گفتار | تشخیص رنگ بصری | بینایی دور | دقت کنترل | بیان شفاهی | درک شفاهی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی و عملیات هوافضا | مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | نصابان و تعمیرکاران تجهیزات صوتی و تصویری | تکنسین‌های اویونیک (الکترونیک هوانوردی) | کاردان‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | کاردان‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | تکنسین‌های نورپردازی | تعمیرکاران تجهیزات پزشکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رندش فلز و پلاستیک | آپاراتچی‌های سینما | تکنسین‌های لابراتوار چشم‌پزشکی و عینک‌سازی | کارگران فرایندهای عکاسی و اپراتورهای ماشین‌های چاپ و ظهور عکس | تکنسین‌های فوتونیک | کارشناسان و تکنسین‌های لیتوگرافی و پیش از چاپ | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصاب و تعمیرکار تجهیزات صوتی و تصویری | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مونتاژکاران تجهیزات الکترومکانیکی | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | تکنسین‌های نورپردازی | تعمیرکاران تجهیزات پزشکی | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | آپاراتچی‌ها و تکنسین‌های نمایش فیلم | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک | کارگران و اپراتورهای ماشین‌های فرآوری و چاپ عکس | تکنسین‌های فوتونیک و اپتیک | تکنسین‌ها و کارگران لیتوگرافی و پیش از چاپ | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | یادگیری فعال | شنیدن فعال</t>
+          <t>درک مطلب | تفکر انتقادی | یادگیری فعال | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
+          <t>مکانیک | رایانه و الکترونیک | خدمات مشتری و شخصی | زبان انگلیسی | مهندسی و فناوری | ریاضیات</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | دید نزدیک | چابکی انگشتان | استدلال قیاسی | درک کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | تجسم فضایی | ثبات دست و بازو | چابکی دستی | تمایز رنگ‌ها | دقت کنترل | درک شفاهی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بدن | توجه انتخابی | سرعت درک | انعطاف‌پذیری در ادراک الگوها | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>حساسیت به مسئله | بینایی نزدیک | مهارت انگشتان | استدلال قیاسی | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تجسم | ثبات دست و بازو | مهارت دستی | تشخیص رنگ بصری | دقت کنترل | درک شفاهی | بیان کتبی | بیان شفاهی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک (الکترونیک هوانوردی) | مهندسان زیستی و مهندسان پزشکی | کاردان‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجهیزات حمل و نقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی تعمیرات و نگهداری تاسیسات | کاردان‌ها و تکنسین‌های مهندسی مکانیک | تکنسین‌های ساخت ارتز و پروتز و تجهیزات ارتوپدی | آماده‌سازان و تکنسین‌های استریلیزاسیون تجهیزات پزشکی | کاردان‌ها و تکنسین‌های مهندسی نانوفناوری | تکنسین‌های فوتونیک | تکنسین‌های رباتیک</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | مهندسان پزشکی و بیوانجینیرینگ | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | کارشناسان و تکنسین‌های مهندسی صنایع | مکانیک‌های ماشین‌آلات صنعتی | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان و تکنسین‌های مهندسی مکانیک | تکنسین‌های ساخت پروتز و اعضای مصنوعی پزشکی | متصدیان آماده‌سازی و استریل تجهیزات پزشکی | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک و اپتیک | تکنسین‌های رباتیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | درک مطلب | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مکانیک | هنرهای تجسمی و نمایشی | زبان انگلیسی</t>
+          <t>خدمات مشتری و شخصی | مکانیک | هنرهای زیبا | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت شنوایی | ثبات دست و بازو | چابکی دستی | چابکی انگشتان | دید نزدیک | دقت کنترل | توجه شنوایی | تجسم فضایی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری در ادراک الگوها | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | درک شفاهی | بیان شفاهی | درک کتبی | دید دور | هماهنگی اندام‌های چندگانه | سرعت تشخیص الگوها</t>
+          <t>حساسیت شنوایی | ثبات دست و بازو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | دقت کنترل | توجه شنیداری | تجسم | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری بستار | استدلال استقرایی | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | درک شفاهی | بیان شفاهی | درک کتبی | بینایی دور | هماهنگی چند عضو | سرعت بستار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | کاردان‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | نصابان و تعمیرکاران کنترلرها و شیرآلات صنعتی، به جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و ماشین‌آلات | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات سنگین متحرک، به جز موتور | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | ورق‌کاران و حلبی‌سازان | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تیزکاران و سنگ‌زنان ابزار | تعمیرکاران ساعت‌های مچی و دیواری | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات نجاری و صنایع چوب، به جز اره‌کشی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکاران دوربین و تجهیزات عکاسی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | مونتاژکاران تجهیزات الکترومکانیکی | مونتاژکاران موتور و سایر ماشین‌آلات | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | مکانیک تجهیزات سنگین متحرک | مکانیک و تکنسین شناورهای موتوری | کارگران ورق‌کاری فلزی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تعمیرکاران ساعت‌های مچی و دیواری | تنظیم‌کنندگان، متصدیان و اپراتورهای ماشین‌آلات صنایع چوب به‌جز اره</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | مکانیک | امور دفتری و اداری | مهندسی و فناوری | تولید و فرآوری</t>
+          <t>خدمات مشتری و شخصی | مدیریت و اداره | مکانیک | اداری | مهندسی و فناوری | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>چابکی انگشتان | ثبات دست و بازو | دقت کنترل | دید نزدیک | چابکی دستی | مرتب‌سازی اطلاعات | حساسیت به مسئله | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | بیان شفاهی | درک کتبی | درک شفاهی | توجه انتخابی</t>
+          <t>مهارت انگشتان | ثبات دست و بازو | دقت کنترل | بینایی نزدیک | مهارت دستی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | تجسم | انعطاف‌پذیری دسته‌بندی | بیان شفاهی | درک کتبی | درک شفاهی | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تعمیرکاران دوربین و تجهیزات عکاسی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران سیم‌پیچ | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های برش و اسلایسینگ | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فورجینگ و آهنگری فلز و پلاستیک | پرداخت‌کاران و سنگ‌زنان دستی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رندش فلز و پلاستیک | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های تابندگی و بافندگی نساجی | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | تیزکاران و سنگ‌زنان ابزار</t>
+          <t>تعمیرکاران دوربین و تجهیزات عکاسی | سیم‌پیچ‌ها، نوارپیچ‌ها و پرداخت‌کاران بوبین | سرویس‌کاران و تعمیرکاران دستگاه‌های سکه‌ای، فروش خودکار و بازی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های برش و ورقه‌کنی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان و اپراتورهای ماشین‌های فورجینگ فلز و پلاستیک | پرداخت‌کاران، سنباده‌کاران و سنگ‌زنان دستی | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | مکانیک‌های ماشین‌آلات صنعتی | جواهرسازان و سازندگان مصنوعات فلزی و سنگ‌های قیمتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های بوبین‌پیچی، تابندگی و کشش الیاف | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | زبان انگلیسی | فیزیک | طراحی | خدمات مشتریان و خدمات فردی</t>
+          <t>مکانیک | رایانه و الکترونیک | مهندسی و فناوری | ریاضیات | زبان انگلیسی | فیزیک | طراحی | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | مرتب‌سازی اطلاعات | دید نزدیک | تجسم فضایی | ثبات دست و بازو | چابکی انگشتان | چابکی دستی | دقت کنترل | هماهنگی اندام‌های چندگانه | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | استدلال ریاضی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بینایی نزدیک | تجسم | ثبات دست و بازو | مهارت انگشتان | مهارت دستی | دقت کنترل | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران تجهیزات پزشکی | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تعمیرکاران ساعت‌های مچی و دیواری | کاردان‌ها و تکنسین‌های کالیبراسیون | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | نصابان و تعمیرکاران کنترلرها و شیرآلات صنعتی، به جز درهای مکانیکی | تکنسین‌های اویونیک (الکترونیک هوانوردی) | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات صنعتی | قفل‌سازان و تعمیرکاران گاوصندوق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | کاردان‌ها و تکنسین‌های مهندسی مکانیک | کاردان‌ها و تکنسین‌های مهندسی، به جز نقشه‌کش‌ها، سایر مشاغل | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | نصابان، تعمیرکاران و کارگران خدمات فنی و نگهداری، سایر مشاغل | بازرسان، آزمون‌گران، درجه‌بندان، نمونه‌گیران و توزین‌گران | تکنسین‌های لابراتوار چشم‌پزشکی و عینک‌سازی</t>
+          <t>تعمیرکاران دوربین و تجهیزات عکاسی | تعمیرکاران تجهیزات پزشکی | تعمیرکاران و کوک‌کنندگان سازهای موسیقی | تعمیرکاران ساعت‌های مچی و دیواری | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تکنسین‌های اویونیک و الکترونیک پرواز | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | قفل‌سازان و تعمیرکاران گاوصندوق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های مهندسی مکانیک | سایر تکنسین‌ها و کارشناسان فنی مهندسی (به‌جز نقشه‌کشان) | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سایر کارگران و تکنسین‌های نصب، نگهداری و تعمیرات | بازرسان، آزمونگران، تفکیک‌کنندگان، نمونه‌برداران و توزین‌گران | تکنسین‌های آزمایشگاه و کارگاه ساخت عینک و قطعات اپتیک</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | شنیدن فعال | درک مطلب</t>
+          <t>تفکر انتقادی | یادگیری فعال | نظارت | سخن گفتن | گوش دادن فعال | درک مطلب</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مکانیک | زبان انگلیسی | ساختمان و سازه | ریاضیات | تولید و فرآوری</t>
+          <t>مکانیک | زبان انگلیسی | ساختمان و ساخت‌وساز | ریاضیات | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>مرتب‌سازی اطلاعات | ثبات دست و بازو | چابکی دستی | دید نزدیک | حساسیت به مسئله | دقت کنترل | تجسم فضایی | بیان شفاهی | درک شفاهی | استدلال قیاسی | چابکی انگشتان | هماهنگی اندام‌های چندگانه | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بدن | توجه انتخابی | انعطاف‌پذیری در ادراک الگوها | انعطاف‌پذیری طبقه‌بندی | استدلال استقرایی | بیان کتبی | تمایز رنگ‌ها | دید دور | تعادل کلی بدن | هماهنگی حرکتی کل بدن | توان و استقامت عضلانی تنه | قدرت عضلانی ایستا | سرعت درک | درک کتبی | حساسیت شنوایی</t>
+          <t>ترتیب‌دهی اطلاعات | ثبات دست و بازو | مهارت دستی | بینایی نزدیک | حساسیت به مسئله | دقت کنترل | تجسم | بیان شفاهی | درک شفاهی | استدلال قیاسی | مهارت انگشتان | هماهنگی چند عضو | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | توجه انتخابی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | تشخیص رنگ بصری | بینایی دور | تعادل کلی بدن | هماهنگی کلی بدن | قدرت تنه | قدرت ایستا | سرعت ادراکی | درک کتبی | حساسیت شنوایی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | دیگ‌سازان و سازندگان مخازن تحت فشار | نصابان و تعمیرکاران کنترلرها و شیرآلات صنعتی، به جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجهیزات حمل و نقل | تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجاری و صنعتی | مونتاژکاران موتور و ماشین‌آلات | مدیران تاسیسات و ساختمان | مکانیک‌ها و تکنسین‌های خدمات ماشین‌آلات کشاورزی | مکانیک‌ها و نصابان سیستم‌های سرمایشی، گرمایشی و تهویه مطبوع (HVAC) | کمک‌برق‌کاران | کمک‌نصابان و کارگران کمکی نگهداری و تعمیرات | کمک‌لوله‌کش‌ها و کارگران کمکی تاسیسات لوله‌کشی | تکنسین‌های نیروگاه‌های برق‌آبی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات صنعتی | ماشین‌سازان صنعتی و نصابان ماشین‌آلات سنگین (میل‌رایت) | مکانیک‌های ماشین‌آلات سنگین متحرک، به جز موتور | لوله‌کش‌ها، نصابان لوله و اتصالات | مهندسان تاسیسات و اپراتورهای موتورخانه و دیگ‌های بخار</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | دیگ‌سازان و مخزن‌سازان صنعتی | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران موتور و سایر ماشین‌آلات | مدیران امور ساختمان و تأسیسات | مکانیک و تکنسین خدمات ماشین‌آلات کشاورزی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | تکنسین‌های نیروگاه برقابی | مکانیک‌های ماشین‌آلات صنعتی | کارگران تعمیر و نگهداری ماشین‌آلات | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | مکانیک تجهیزات سنگین متحرک | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | شنیدن فعال | سخن گفتن | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | گوش دادن فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مکانیک | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | مهندسی و فناوری | آموزش و تدریس | مدیریت و امور اداری | ریاضیات | ساختمان و سازه | فیزیک</t>
+          <t>مکانیک | رایانه و الکترونیک | زبان انگلیسی | ایمنی و امنیت عمومی | مهندسی و فناوری | آموزش و پرورش | مدیریت و اداره | ریاضیات | ساختمان و ساخت‌وساز | فیزیک</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | چابکی انگشتان | دید نزدیک | ثبات دست و بازو | چابکی دستی | استدلال قیاسی | دقت کنترل | هماهنگی اندام‌های چندگانه | درک کتبی | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | تجسم فضایی | دید دور | تعادل کلی بدن | انعطاف‌پذیری بدن | توان و استقامت عضلانی تنه | قدرت بدنی پویا | توجه انتخابی | سرعت درک | انعطاف‌پذیری در ادراک الگوها | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنوایی | استقامت بدنی | قدرت عضلانی ایستا | زمان واکنش | بیان کتبی</t>
+          <t>حساسیت به مسئله | درک شفاهی | مهارت انگشتان | بینایی نزدیک | ثبات دست و بازو | مهارت دستی | استدلال قیاسی | دقت کنترل | هماهنگی چند عضو | درک کتبی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تجسم | بینایی دور | تعادل کلی بدن | انعطاف‌پذیری دامنه حرکت | قدرت تنه | قدرت پویا | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه شنیداری | استقامت | قدرت ایستا | زمان عکس‌العمل | بیان کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های اویونیک (الکترونیک هوانوردی) | تکنسین‌های نیروگاه‌های زیست‌توده (بیومس) | نصابان و تعمیرکاران کنترلرها و شیرآلات صنعتی، به جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مهندسان برق | تعمیرکاران تجهیزات الکتریکی و الکترونیکی نیروگاه‌ها، پست‌ها و رله‌ها | اپراتورهای تأسیسات گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های انرژی زمین‌گرمایی | تکنسین‌های نیروگاه‌های برق‌آبی | مدیران تولید برق‌آبی | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های فتوولتائیک خورشیدی | نصابان و تکنسین‌های سیستم‌های حرارتی خورشیدی | مهندسان تاسیسات و اپراتورهای موتورخانه و دیگ‌های بخار | مدیران توسعه انرژی بادی | مهندسان انرژی بادی | مدیران عملیات پروژه‌های انرژی بادی</t>
+          <t>تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌های نیروگاه زیست‌توده | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مهندسان برق | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | اپراتورهای تأسیسات و پالایشگاه‌های گاز | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مهندسان سیستم‌های انرژی خورشیدی | نصابان سیستم‌های خورشیدی فتوولتائیک | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال</t>
+          <t>نظارت | تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | مکانیک | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | مکانیک | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>چابکی دستی | چابکی انگشتان | ثبات دست و بازو | دید نزدیک | دقت کنترل | مرتب‌سازی اطلاعات | هماهنگی اندام‌های چندگانه | تجسم فضایی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | درک کتبی</t>
+          <t>مهارت دستی | مهارت انگشتان | ثبات دست و بازو | بینایی نزدیک | دقت کنترل | ترتیب‌دهی اطلاعات | هماهنگی چند عضو | تجسم | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | توجه انتخابی | درک کتبی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اپراتورها و متصدیان دستگاه‌های اتصال چسبی | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های اکستروژن و فرم‌دهی الیاف مصنوعی و شیشه | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرم‌دهی، پرس و فشرده‌سازی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های سنگ‌زنی، لپینگ، پولیش و پرداخت فلز و پلاستیک | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و متصدیان تخلیه ماشین‌آلات خط تولید | کارگران تعمیر و نگهداری ماشین‌آلات صنعتی | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌های فرز و رندش فلز و پلاستیک | مکانیک‌های ماشین‌آلات سنگین متحرک، به جز موتور | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌ابزارهای چندکاره فلز و پلاستیک | متصدیان ماشین‌های اداری، به جز رایانه | اپراتورها و متصدیان دستگاه‌های بسته‌بندی و پرکن | تنظیم‌کنندگان، اپراتورها و متصدیان ماشین‌آلات تولید محصولات کاغذی | تیزکاران و سنگ‌زنان ابزار | تعمیرکاران ساعت‌های مچی و دیواری</t>
+          <t>اپراتورها و متصدیان ماشین‌های چسب‌زنی و اتصال | تعمیرکاران رایانه، خودپرداز و ماشین‌های اداری | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | مونتاژکاران تجهیزات الکترومکانیکی | تنظیم‌کنندگان، اپراتورها و مراقبان ماشین‌های اکستروژن و شکل‌دهی الیاف مصنوعی و شیشه‌ای | تنظیم‌کنندگان، اپراتورها و متصدیان دستگاه‌های اکستروژن، فرم‌دهی، پرس و تراکم مواد | تنظیم‌کاران و اپراتورهای ماشین‌های سنگ‌زنی، پرداخت، صیقل‌کاری و براق‌کاری فلز و پلاستیک | تعمیرکاران لوازم خانگی | مکانیک‌های ماشین‌آلات صنعتی | تنظیم‌کاران و اپراتورهای ماشین‌های تراشکاری فلز و پلاستیک | تغذیه‌کنندگان و تخلیه‌کنندگان ماشین‌آلات | کارگران تعمیر و نگهداری ماشین‌آلات | تنظیم‌کاران و اپراتورهای ماشین‌های فرز و صفحه‌تراش فلز و پلاستیک | مکانیک تجهیزات سنگین متحرک | تنظیم‌کاران و اپراتورهای ماشین‌ابزارهای چندگانه فلز و پلاستیک | اپراتورهای ماشین‌آلات اداری، به‌جز رایانه | اپراتورها و متصدیان ماشین‌های بسته‌بندی و پرکن | تنظیم‌کنندگان و اپراتورهای ماشین‌های تولید محصولات کاغذی | سنگ‌زن‌ها، سوهان‌کاران و تیزکاران ابزار | تعمیرکاران ساعت‌های مچی و دیواری</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مکانیک | ساختمان و سازه | فیزیک | خدمات مشتریان و خدمات فردی | ریاضیات | ایمنی و امنیت عمومی | آموزش و تدریس</t>
+          <t>مکانیک | ساختمان و ساخت‌وساز | فیزیک | خدمات مشتری و شخصی | ریاضیات | ایمنی و امنیت عمومی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | هماهنگی اندام‌های چندگانه | چابکی دستی | چابکی انگشتان | دید نزدیک | تشخیص گفتار | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال استقرایی | انعطاف‌پذیری بدن | سرعت درک | درک کتبی | انعطاف‌پذیری در ادراک الگوها | قدرت عضلانی ایستا | دید دور | درک عمق | وضوح گفتار | تمایز رنگ‌ها | استقامت بدنی | توان و استقامت عضلانی تنه | زمان واکنش | تقسیم توجه | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری طبقه‌بندی | قدرت بدنی پویا | جهت‌گیری واکنشی | جهت‌یابی فضایی | ابتکار | روانی ایده‌ها | بیان کتبی | تعادل کلی بدن | هماهنگی حرکتی کل بدن</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | ثبات دست و بازو | دقت کنترل | هماهنگی چند عضو | مهارت دستی | مهارت انگشتان | بینایی نزدیک | تشخیص گفتار | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال استقرایی | انعطاف‌پذیری دامنه حرکت | سرعت ادراکی | درک کتبی | انعطاف‌پذیری بستار | قدرت ایستا | بینایی دور | درک عمق | وضوح گفتار | تشخیص رنگ بصری | استقامت | قدرت تنه | زمان عکس‌العمل | تقسیم توجه | توجه انتخابی | تجسم | انعطاف‌پذیری دسته‌بندی | قدرت پویا | جهت‌گیری پاسخ | جهت‌گیری فضایی | اصالت | روانی ایده‌ها | بیان کتبی | تعادل کلی بدن | هماهنگی کلی بدن</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>دیگ‌سازان و سازندگان مخازن تحت فشار | کارگران ساختمانی | اپراتورهای لایروب | حفاران زمین، به جز نفت و گاز | اپراتورهای ماشین‌های حفاری، بارگیری و دراگلاین در معادن روباز | کمک‌برق‌کاران | کمک‌لوله‌کش‌ها و کارگران کمکی تاسیسات لوله‌کشی | اپراتورهای بالابر و وینچ | مهندسان دریایی و معماران کشتی | مکانیک‌های ماشین‌آلات سنگین متحرک، به جز موتور | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | لوله‌گذاران | لوله‌کش‌ها، نصابان لوله و اتصالات | ریگرها و متصدیان بستن و مهار بار (طناب‌بندها) | اپراتورهای دکل‌های حفاری دورانی نفت و گاز | کارگران فنی سکوهای حفاری نفت و گاز (راستابات) | ملوانان و نیروهای موتورخانه شناورها | سرویس‌کاران چاه‌های سپتیک و پاک‌کنندگان خطوط فاضلاب | مهندسان کشتی و شناور | جوشکاران، برشکاران، لحیم‌کاران سخت و نرم</t>
+          <t>دیگ‌سازان و مخزن‌سازان صنعتی | کارگران ساختمانی | اپراتورهای لایروب | حفاران زمین، به‌جز نفت و گاز | اپراتورهای ماشین‌آلات حفاری، بارگیری و درگ‌لاین در معادن روباز | کمک‌برق‌کاران | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | اپراتورهای بالابر و وینچ | مهندسان دریایی و معماران کشتی | مکانیک تجهیزات سنگین متحرک | اپراتورهای ماشین‌آلات سنگین و تجهیزات عمرانی | لوله‌گذاران خطوط انتقال | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | حفاران دورانی نفت و گاز | کارگران عمومی سکو و میادین نفت و گاز | ملوانان و روغن‌کاران شناورهای دریایی | سرویس‌کاران مخازن سپتیک و لایروبان مجاری فاضلاب | مهندسان فنی کشتی | جوشکاران، برشکاران و لحیم‌کاران صنعتی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مکانیک | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | زبان انگلیسی | مدیریت و امور اداری | حقوق و مقررات دولتی | فروش و بازاریابی | آموزش و تدریس | ریاضیات | رایانه و الکترونیک | امور دفتری و اداری | اقتصاد و حسابداری | ساختمان و سازه</t>
+          <t>مکانیک | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | زبان انگلیسی | مدیریت و اداره | قانون و دولت | فروش و بازاریابی | آموزش و پرورش | ریاضیات | رایانه و الکترونیک | اداری | اقتصاد و حسابداری | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>ثبات دست و بازو | دید نزدیک | چابکی انگشتان | تجسم فضایی | دقت کنترل | بیان شفاهی | چابکی دستی | مرتب‌سازی اطلاعات | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | استدلال استقرایی | بیان کتبی | توجه انتخابی | سرعت درک | انعطاف‌پذیری در ادراک الگوها | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری بدن | توان و استقامت عضلانی تنه | هماهنگی اندام‌های چندگانه</t>
+          <t>ثبات دست و بازو | بینایی نزدیک | مهارت انگشتان | تجسم | دقت کنترل | بیان شفاهی | مهارت دستی | ترتیب‌دهی اطلاعات | استدلال قیاسی | حساسیت به مسئله | درک شفاهی | استدلال استقرایی | بیان کتبی | توجه انتخابی | سرعت ادراکی | انعطاف‌پذیری بستار | درک کتبی | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دامنه حرکت | قدرت تنه | هماهنگی چند عضو</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مونتاژکاران سازه، سطوح، اتصالات و سیستم‌های هواپیما | نصابان و تعمیرکاران شیشه خودرو | نصابان و تعمیرکاران کنترلرها و شیرآلات صنعتی، به جز درهای مکانیکی | تعمیرکاران الکتروموتورها، ابزارهای برقی و ادوات وابسته | نصابان و تعمیرکاران تجهیزات الکتریکی و الکترونیکی تجهیزات حمل و نقل | برق‌کاران | نصابان و تعمیرکاران تجهیزات الکترونیکی خودرو | نصابان و تعمیرکاران آسانسور و پله‌برقی | مونتاژکاران موتور و ماشین‌آلات | کمک‌برق‌کاران | کمک‌نصابان و کارگران کمکی نگهداری و تعمیرات | کمک‌لوله‌کش‌ها و کارگران کمکی تاسیسات لوله‌کشی | تعمیرکاران لوازم خانگی | کارگران عمومی تعمیرات و نگهداری تاسیسات | تعمیرکاران درهای مکانیکی و اتوماتیک | ماشین‌سازان صنعتی و نصابان ماشین‌آلات سنگین (میل‌رایت) | لوله‌کش‌ها، نصابان لوله و اتصالات | ریگرها و متصدیان بستن و مهار بار (طناب‌بندها) | نصابان سیستم‌های اعلام سرقت و حریق | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی</t>
+          <t>مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | نصاب و تعمیرکار شیشه خودرو | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | تعمیرکاران موتورهای الکتریکی، ابزارهای برقی و تجهیزات وابسته | نصاب و تعمیرکار تجهیزات الکتریکی و الکترونیکی وسایل نقلیه | برق‌کاران | نصاب و تعمیرکار تجهیزات الکترونیکی وسایل نقلیه موتوری | نصابان و تعمیرکاران آسانسور و پله‌برقی | مونتاژکاران موتور و سایر ماشین‌آلات | کمک‌برق‌کاران | کارگران کمکی نصب، نگهداری و تعمیرات | کمک‌لوله‌گذاران، کمک‌لوله‌کش‌ها، کمک‌نصابان لوله و بخار | تعمیرکاران لوازم خانگی | کارگران عمومی تعمیرات و نگهداری تاسیسات | تعمیرکاران درب‌های مکانیکی و اتوماتیک | ماشین‌سازان و متخصصان نصب ماشین‌آلات سنگین [میل‌رایت] | لوله‌کش‌ها، لوله‌کش‌های صنعتی و نصابان خطوط بخار | ریگرها و تکنسین‌های مهاربندی و جابه‌جایی بار | نصاب سیستم‌های اعلام سرقت و حریق | مونتاژکاران و تنظیم‌کنندگان ادوات زمان‌سنجی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
